--- a/src/test/resources/mock/test-update-another-grade.xlsx
+++ b/src/test/resources/mock/test-update-another-grade.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>ref</t>
   </si>
@@ -25,9 +25,6 @@
   </si>
   <si>
     <t>STD22031</t>
-  </si>
-  <si>
-    <t>STD22033</t>
   </si>
 </sst>
 </file>
@@ -583,12 +580,7 @@
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
-        <v>18</v>
-      </c>
+      <c r="B3" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
